--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T08:52:11+00:00</t>
+    <t>2025-10-05T20:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-05T20:06:33+00:00</t>
+    <t>2025-10-05T20:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-05T20:13:42+00:00</t>
+    <t>2025-10-06T08:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-06T08:31:06+00:00</t>
+    <t>2025-10-09T18:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T18:55:57+00:00</t>
+    <t>2025-10-09T19:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T19:07:52+00:00</t>
+    <t>2025-10-09T19:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T19:37:50+00:00</t>
+    <t>2025-10-09T19:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T19:58:38+00:00</t>
+    <t>2026-01-29T20:13:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T20:13:56+00:00</t>
+    <t>2026-03-07T08:52:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T08:52:42+00:00</t>
+    <t>2026-03-07T09:02:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T09:02:29+00:00</t>
+    <t>2026-03-07T09:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T09:32:39+00:00</t>
+    <t>2026-03-07T09:45:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T09:45:24+00:00</t>
+    <t>2026-03-13T10:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T10:43:11+00:00</t>
+    <t>2026-05-08T07:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
+    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T07:00:45+00:00</t>
+    <t>2026-05-08T07:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T07:11:48+00:00</t>
+    <t>2026-05-08T08:25:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T08:25:34+00:00</t>
+    <t>2026-05-08T08:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T08:40:16+00:00</t>
+    <t>2026-05-08T09:06:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:06:57+00:00</t>
+    <t>2026-05-08T09:33:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:33:11+00:00</t>
+    <t>2026-05-08T10:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:00:47+00:00</t>
+    <t>2026-05-08T10:09:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:09:24+00:00</t>
+    <t>2026-05-08T11:19:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T11:19:22+00:00</t>
+    <t>2026-05-08T15:55:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T15:55:34+00:00</t>
+    <t>2026-06-26T06:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsRespirationRateDepthValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T06:37:03+00:00</t>
+    <t>2026-06-26T06:47:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
